--- a/docs/video_manual/v1.6/exports/Report_Depot-wise_Freight.xlsx
+++ b/docs/video_manual/v1.6/exports/Report_Depot-wise_Freight.xlsx
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 18-10-2026 00:47 by Master Administrator</t>
+          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 21-10-2026 05:16 by Master Administrator</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
         <v>92350</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>433.35</v>
+        <v>433.33</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>0</v>
@@ -662,7 +662,7 @@
         <v>47700</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>666.67</v>
+        <v>616.67</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>13</v>
@@ -698,7 +698,7 @@
         <v>43900</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>0</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>24</v>
@@ -734,7 +734,7 @@
         <v>77700</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>300</v>
+        <v>426</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
@@ -753,7 +753,7 @@
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>127</v>
@@ -762,7 +762,7 @@
         <v>428700</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>2456.02</v>
+        <v>2637</v>
       </c>
       <c r="H11" s="8" t="n">
         <v>0</v>

--- a/docs/video_manual/v1.6/exports/Report_Depot-wise_Freight.xlsx
+++ b/docs/video_manual/v1.6/exports/Report_Depot-wise_Freight.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,11 @@
       <i val="1"/>
       <color rgb="005B6675"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -70,18 +75,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -472,57 +478,60 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 21-10-2026 05:16 by Master Administrator</t>
-        </is>
-      </c>
+          <t>Tulsyan (Demonstration) · 01-10-2026 to … (Invoice date) · generated 21-10-2026 14:47 by Master Administrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Depot</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Principal</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Dispatch Count</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Boxes</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Sales</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Calculated Freight</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Actual Freight (billed)</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Calculated (billed inv.)</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
@@ -544,25 +553,25 @@
           <t>ABC Pharma Ltd (Demo)</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>135850</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>704</v>
       </c>
-      <c r="H5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -580,25 +589,25 @@
           <t>PQR Lifesciences Ltd (Demo)</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>31200</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <v>220</v>
       </c>
-      <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -616,25 +625,25 @@
           <t>ABC Pharma Ltd (Demo)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <v>92350</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>433.33</v>
       </c>
-      <c r="H7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="5" t="inlineStr"/>
+      <c r="H7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -652,25 +661,25 @@
           <t>XYZ Healthcare Ltd (Demo)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <v>47700</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <v>616.67</v>
       </c>
-      <c r="H8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr"/>
+      <c r="H8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -688,25 +697,25 @@
           <t>PQR Lifesciences Ltd (Demo)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="6" t="n">
         <v>43900</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="6" t="n">
         <v>237</v>
       </c>
-      <c r="H9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr"/>
+      <c r="H9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -724,53 +733,53 @@
           <t>XYZ Healthcare Ltd (Demo)</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="6" t="n">
         <v>77700</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="6" t="n">
         <v>426</v>
       </c>
-      <c r="H10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr"/>
+      <c r="H10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="7" t="n">
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="E11" s="7" t="n">
+      <c r="E11" s="8" t="n">
         <v>127</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="9" t="n">
         <v>428700</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="9" t="n">
         <v>2637</v>
       </c>
-      <c r="H11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8" t="n"/>
+      <c r="H11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:J11"/>
